--- a/docs/export-templates/AI问书_全域模型用量数据导出.xlsx
+++ b/docs/export-templates/AI问书_全域模型用量数据导出.xlsx
@@ -22,7 +22,7 @@
     <t>导出时间：2026-07-14 10:00:00 · 实时统计时间：2026-07-14 10:00:00 · 平台开通至今累计，实时快照、不参与环比</t>
   </si>
   <si>
-    <t>筛选条件：机构范围＝全部 · 时间区间＝近 7 天</t>
+    <t>筛选条件：机构范围＝全部机构 · 时间区间＝近 7 天</t>
   </si>
   <si>
     <t>指标</t>
@@ -46,7 +46,7 @@
     <t>token</t>
   </si>
   <si>
-    <t>平台默认 LLM 输入+输出累计</t>
+    <t>平台默认 LLM 输入+输出累计（所选机构累加）</t>
   </si>
   <si>
     <t>累计调用次数</t>
@@ -58,13 +58,13 @@
     <t>次</t>
   </si>
   <si>
-    <t>平台默认 LLM 被请求总次数</t>
+    <t>平台默认 LLM 被请求总次数（所选机构累加）</t>
   </si>
   <si>
     <t>平台全域模型用量 · 区间指标（近 7 天）</t>
   </si>
   <si>
-    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-31 ~ 2026-08-06） · 机构范围=全部</t>
+    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-09-12 ~ 2026-09-18） · 机构范围=全部机构</t>
   </si>
   <si>
     <t>较上一周期</t>
@@ -79,7 +79,7 @@
     <t>↑ +9.2%</t>
   </si>
   <si>
-    <t>输入+输出</t>
+    <t>输入+输出（所选机构累加）</t>
   </si>
   <si>
     <t>区间调用次数</t>
@@ -91,7 +91,7 @@
     <t>↑ +6.1%</t>
   </si>
   <si>
-    <t>模型请求</t>
+    <t>模型请求（所选机构累加）</t>
   </si>
   <si>
     <t>平均响应</t>
@@ -106,13 +106,13 @@
     <t>↓ 缩短 0.2 秒</t>
   </si>
   <si>
-    <t>请求到首字</t>
+    <t>请求到首字（均值类，不累加）</t>
   </si>
   <si>
     <t>模型用量趋势 · 近 7 天</t>
   </si>
   <si>
-    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-31 ~ 2026-08-06）</t>
+    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-09-12 ~ 2026-09-18）</t>
   </si>
   <si>
     <t>时间</t>
@@ -130,7 +130,7 @@
     <t>250万</t>
   </si>
   <si>
-    <t>全部</t>
+    <t>全部机构</t>
   </si>
   <si>
     <t>05-26</t>
@@ -178,7 +178,7 @@
     <t>Token 用量</t>
   </si>
   <si>
-    <t>XX 出版社</t>
+    <t>XX 出版集团</t>
   </si>
   <si>
     <t>640万</t>
